--- a/Audit/JJ_PM_SC02_요구사항정의서_v1.4_20261028_이노팸.xlsx
+++ b/Audit/JJ_PM_SC02_요구사항정의서_v1.4_20261028_이노팸.xlsx
@@ -12,83 +12,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항정의서_기능" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항정의서_비기능" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_">#REF!</definedName>
-    <definedName name="__">#REF!</definedName>
-    <definedName name="_80486SX_25">[1]COST!#REF!</definedName>
     <definedName name="_kwy1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_L80486SX_25">[1]COST!#REF!</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="_Order2" hidden="1">255</definedName>
-    <definedName name="_SX25">[1]COST!#REF!</definedName>
-    <definedName name="_Table1_In1" hidden="1">#REF!</definedName>
-    <definedName name="_Table1_Out" hidden="1">#REF!</definedName>
-    <definedName name="_wo1">'[2]예정(3)'!#REF!</definedName>
-    <definedName name="\0">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="\A">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="\B">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="\I">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="\O">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="\P">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="\Q">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="A">#REF!</definedName>
-    <definedName name="A000">#REF!</definedName>
-    <definedName name="a2121212">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="AA" hidden="1">#REF!</definedName>
-    <definedName name="AAA">#REF!</definedName>
-    <definedName name="AAAA">#REF!</definedName>
-    <definedName name="AAAAA">#REF!</definedName>
-    <definedName name="add">#REF!</definedName>
-    <definedName name="ARSCC">#REF!</definedName>
-    <definedName name="ASIC">#REF!</definedName>
-    <definedName name="b">[4]단계별측정!#REF!</definedName>
-    <definedName name="baseline">[10]CSR납기분석!#REF!</definedName>
-    <definedName name="bb">'[3]9GNG운반'!#REF!</definedName>
-    <definedName name="BTSINFO_991Q">#REF!</definedName>
-    <definedName name="BTSINFO_992Q">#REF!</definedName>
-    <definedName name="BTSINFO_팀구분">#REF!</definedName>
-    <definedName name="C80486DX_33">[1]COST!#REF!</definedName>
-    <definedName name="C80486DX_50">[1]COST!#REF!</definedName>
-    <definedName name="C80486DX2_50">[1]COST!#REF!</definedName>
-    <definedName name="C80486DX2_66">[1]COST!#REF!</definedName>
-    <definedName name="C80486SX_25">[1]COST!#REF!</definedName>
-    <definedName name="C80486SX_33">[1]COST!#REF!</definedName>
-    <definedName name="CAMPC">#REF!</definedName>
-    <definedName name="cause">#REF!</definedName>
-    <definedName name="CB_1">#REF!</definedName>
-    <definedName name="change_age">#REF!</definedName>
-    <definedName name="change_no">#REF!</definedName>
-    <definedName name="CHC_경기">#REF!</definedName>
-    <definedName name="CHC_서울">#REF!</definedName>
-    <definedName name="CHC_서울_COUNT">#REF!</definedName>
-    <definedName name="CHC산출_경기">'[11]Calc V1.2'!$H$1:$AC$65536</definedName>
-    <definedName name="CHC산출_서울">'[11]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
-    <definedName name="Comments">#REF!</definedName>
-    <definedName name="cost_a">#REF!</definedName>
-    <definedName name="cost_b">#REF!</definedName>
-    <definedName name="cost_e">#REF!</definedName>
     <definedName name="cwe" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="D" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_xlnm.Database">#REF!</definedName>
-    <definedName name="DC_서울">#REF!</definedName>
-    <definedName name="dd">#REF!</definedName>
     <definedName name="DJDJDJDJ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="dk" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="dkjdlfw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -96,52 +25,12 @@
     <definedName name="dkw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="DocumentName">"OE-TS-UTR-001"</definedName>
     <definedName name="dsfga" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="DTIC">#REF!</definedName>
-    <definedName name="e">[4]단계별측정!#REF!</definedName>
-    <definedName name="ee">[4]단계별측정!#REF!</definedName>
-    <definedName name="eeeeee">[4]단계별측정!#REF!</definedName>
-    <definedName name="effort_a">#REF!</definedName>
-    <definedName name="effort_change">#REF!</definedName>
-    <definedName name="effort_e">#REF!</definedName>
-    <definedName name="effort_review">#REF!</definedName>
-    <definedName name="effort_rework">#REF!</definedName>
-    <definedName name="EI_A">IF( OR(AND(#REF!&lt;2,#REF!&gt;50), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 20,#REF!&lt;= 50)), AND(#REF!&gt;5, AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
-    <definedName name="EI_C">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=5),#REF!&gt; 50), AND(#REF!&gt;5,#REF!&gt;=  20) ),1,0)</definedName>
-    <definedName name="EI_first_row">#REF!</definedName>
-    <definedName name="EI_Name">#REF!</definedName>
-    <definedName name="EI_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 50)), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
-    <definedName name="ENG_Data">#REF!</definedName>
-    <definedName name="ENG_Data_서울">#REF!</definedName>
-    <definedName name="ENG_Data_증설후">#REF!</definedName>
-    <definedName name="ENG_개체전">#REF!</definedName>
-    <definedName name="ENG_개체후">#REF!</definedName>
-    <definedName name="ENG11차">#REF!</definedName>
-    <definedName name="ENGDATA">#REF!</definedName>
-    <definedName name="Entity_List">#REF!</definedName>
     <definedName name="er" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="Est_Eff_MDay">[12]FPA!#REF!</definedName>
-    <definedName name="ex_rate">#REF!</definedName>
-    <definedName name="FA_서울">#REF!</definedName>
-    <definedName name="fdssdsdfds">#REF!</definedName>
-    <definedName name="FF" hidden="1">#REF!</definedName>
     <definedName name="fkwheku" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="FT_A">IF( OR(AND(#REF!&lt;2,#REF!&gt;50), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 20,#REF!&lt;= 50)), AND(#REF!&gt;5, AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
-    <definedName name="FT_C">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=5),#REF!&gt; 50), AND(#REF!&gt;5,#REF!&gt;=  20) ),1,0)</definedName>
-    <definedName name="FT_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 50)), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
-    <definedName name="Function_List">#REF!</definedName>
-    <definedName name="GFACTOR_9901기준">#REF!</definedName>
     <definedName name="gfdsdfg" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="GSTC">#REF!</definedName>
     <definedName name="H" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="hejlkw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="hsdgfjhf" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ICPC">#REF!</definedName>
-    <definedName name="Index">'[13]Data Vol'!$B$6:$E$6816</definedName>
-    <definedName name="IT_A">IF( OR(AND(#REF!&lt;2,#REF!&gt;15), AND(#REF!=2, AND(#REF!&gt;= 5,#REF!&lt;= 15)), AND(#REF!&gt;2, AND(#REF!&gt;=1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="IT_C">IF( OR(AND(#REF!=2,#REF!&gt; 15), AND(#REF!&gt;2,#REF!&gt;=  5) ),1,0)</definedName>
-    <definedName name="IT_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 15)), AND(#REF!=2, AND(#REF!&gt;= 1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="itsa_ratio_nrec">[14]공수견적!#REF!</definedName>
-    <definedName name="itsa_ratio_rec">[12]순수개발!#REF!</definedName>
     <definedName name="IWFIC" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jdkl" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jeklw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -153,69 +42,13 @@
     <definedName name="kljdklw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="klwjdk" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="kwy" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="L80486SX_25"> [1]COST!#REF!</definedName>
-    <definedName name="LastRow">#REF!</definedName>
-    <definedName name="LPA_서울">#REF!</definedName>
-    <definedName name="LRIC">#REF!</definedName>
     <definedName name="Ltst_TestLog">"'Test log'"</definedName>
-    <definedName name="M">#REF!</definedName>
-    <definedName name="Modifier">#REF!</definedName>
-    <definedName name="MSIC">#REF!</definedName>
-    <definedName name="MSICC">#REF!</definedName>
-    <definedName name="MTC">#REF!</definedName>
-    <definedName name="name">[7]IN!$D$5</definedName>
-    <definedName name="name1">[7]IN!$D$5</definedName>
-    <definedName name="NESC">#REF!</definedName>
-    <definedName name="NO">#REF!</definedName>
-    <definedName name="OCPC">#REF!</definedName>
-    <definedName name="oo">'[2]동원(3)'!#REF!</definedName>
-    <definedName name="OT_A">IF( OR(AND(#REF!&lt;2,#REF!&gt;19), AND(AND(#REF!&gt;=2,#REF!&lt;= 3), AND(#REF!&gt;= 6,#REF!&lt;= 19)), AND(#REF!&gt;3, AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
-    <definedName name="OT_C">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=3),#REF!&gt; 19), AND(#REF!&gt;3,#REF!&gt;=  6) ),1,0)</definedName>
-    <definedName name="OT_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 19)), AND(AND(#REF!&gt;=2,#REF!&lt;=3), AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
-    <definedName name="PAP">#REF!</definedName>
     <definedName name="PERT" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="PRICE">[1]COST!#REF!</definedName>
-    <definedName name="Q">#REF!</definedName>
     <definedName name="qq" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="QT_A">IF( OR(AND(#REF!&lt;2,#REF!&gt;19), AND(AND(#REF!&gt;=2,#REF!&lt;= 3), AND(#REF!&gt;= 6,#REF!&lt;= 19)), AND(#REF!&gt;3, AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
-    <definedName name="QT_C">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=3),#REF!&gt; 19), AND(#REF!&gt;3,#REF!&gt;=  6) ),1,0)</definedName>
-    <definedName name="QT_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 19)), AND(AND(#REF!&gt;=2,#REF!&lt;=3), AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
-    <definedName name="RC0_서울">#REF!</definedName>
-    <definedName name="_xlnm.Recorder">#REF!</definedName>
-    <definedName name="req_added">#REF!</definedName>
-    <definedName name="req_base">#REF!</definedName>
-    <definedName name="req_changed">#REF!</definedName>
-    <definedName name="req_deleted">#REF!</definedName>
-    <definedName name="review_defect">#REF!</definedName>
-    <definedName name="review_error">#REF!</definedName>
-    <definedName name="RMS">#REF!</definedName>
-    <definedName name="rpt_date">[15]요약!$C$4</definedName>
-    <definedName name="rr" hidden="1">#REF!</definedName>
-    <definedName name="RRR" hidden="1">#REF!</definedName>
     <definedName name="s" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="SCDLC">#REF!</definedName>
-    <definedName name="schedule_a_e">#REF!</definedName>
-    <definedName name="schedule_a_s">#REF!</definedName>
-    <definedName name="schedule_e_e">#REF!</definedName>
-    <definedName name="schedule_e_s">#REF!</definedName>
-    <definedName name="SEC_서울">#REF!</definedName>
-    <definedName name="Severity">#REF!</definedName>
-    <definedName name="size_code_e">[4]소스코드크기측정!#REF!</definedName>
-    <definedName name="SS" hidden="1">#REF!</definedName>
-    <definedName name="SSD">#REF!</definedName>
-    <definedName name="SSN7C">#REF!</definedName>
-    <definedName name="staffDay">#REF!</definedName>
-    <definedName name="staffMonth">#REF!</definedName>
-    <definedName name="staffWeek">#REF!</definedName>
-    <definedName name="State_of_Origin">#REF!</definedName>
-    <definedName name="tol">'[10]규모,공수분석'!#REF!</definedName>
     <definedName name="TOTAL" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="tt" hidden="1">#REF!</definedName>
-    <definedName name="TTT">#REF!</definedName>
-    <definedName name="US">[1]COST!$P$2</definedName>
     <definedName name="vbkjwhe" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vdwf" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="Version">#REF!</definedName>
     <definedName name="vewtf" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vhjkwghe" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vhjkwhe" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -247,7 +80,6 @@
     <definedName name="vwefg" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vwer" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vwvw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="W">#REF!</definedName>
     <definedName name="wd" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="werwe" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="wkeljd" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -255,54 +87,31 @@
     <definedName name="wrn.aaa." hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="wrn.TEST." hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="wte" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ww" hidden="1">#REF!</definedName>
-    <definedName name="zzzzzzzzzzzzzzzzzzz">#REF!</definedName>
     <definedName name="ㄱ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㄱㄱㄷㄱ">#REF!</definedName>
     <definedName name="ㄱㅎㄷㄱㅎ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="개정이력">[4]단계별측정!#REF!</definedName>
-    <definedName name="계획표">#REF!</definedName>
     <definedName name="공사설명서" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업">[5]COST!#REF!</definedName>
-    <definedName name="과업대비표1">#REF!</definedName>
-    <definedName name="국소수_서울">#REF!</definedName>
-    <definedName name="기존프로그램">#REF!</definedName>
-    <definedName name="기준용어">#REF!</definedName>
-    <definedName name="ㄴ" hidden="1">#REF!</definedName>
-    <definedName name="ㄴㄴ">[6]단계별측정!#REF!</definedName>
     <definedName name="ㄴㄴㄱ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴ아러" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="나" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="납기1">[7]IN!$B$5</definedName>
-    <definedName name="납기2">[8]IN!$B$5</definedName>
-    <definedName name="납기3">[7]IN!$D$5</definedName>
-    <definedName name="납기4">[8]IN!$D$5</definedName>
     <definedName name="ㄷ가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄷㄷㄷ">#REF!</definedName>
     <definedName name="다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="단가">#REF!</definedName>
-    <definedName name="도">#REF!</definedName>
     <definedName name="두지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="둑ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄹㅇㅁㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="라" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄻㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁ" hidden="1">#REF!</definedName>
     <definedName name="ㅁㄻㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="ㅁㅁㅁ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="마" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="문서명">"단위시험 결과서"</definedName>
     <definedName name="문서번호표시">"Document #: " &amp; DocumentName</definedName>
-    <definedName name="ㅂ" hidden="1">#REF!</definedName>
     <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="바" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="버전">"Version " &amp; Version</definedName>
     <definedName name="변경내역" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="보" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="분류">#REF!</definedName>
-    <definedName name="ㅅㅅㅅ" hidden="1">#REF!</definedName>
     <definedName name="사" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="수" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="수정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -314,7 +123,6 @@
     <definedName name="수정6" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="시스템명">"IVR시스템 연계 및 개발"</definedName>
     <definedName name="신설변경" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇ45">#REF!</definedName>
     <definedName name="ㅇ나닐ㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅇㄹㅇ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="ㅇㄹㅈㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -328,63 +136,37 @@
     <definedName name="아ㅓㅗㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="알람관리">#REF!</definedName>
-    <definedName name="이력">[4]검토측정!#REF!</definedName>
-    <definedName name="이름" hidden="1">#REF!</definedName>
-    <definedName name="이름1">#REF!</definedName>
-    <definedName name="일반현황__2_">#REF!</definedName>
-    <definedName name="일반현황_3">#REF!</definedName>
     <definedName name="일일대가1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅈㅂㄷㅈㅂㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="자" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="자ㅓㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="재료집계3">#REF!</definedName>
-    <definedName name="전기출력2">[9]ELEC!$B$3:$M$3,[9]ELEC!$B$4:$M$4,[9]ELEC!$B$5:$M$5,[9]ELEC!$B$7:$M$7</definedName>
-    <definedName name="전기출력3">[9]ELEC!$B$3:$M$3,[9]ELEC!$B$6:$M$6,[9]ELEC!$B$8:$M$8</definedName>
     <definedName name="정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="제주추가종합수정안" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="중계기현황">#REF!</definedName>
     <definedName name="지더" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="지두" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="직종">#REF!</definedName>
     <definedName name="차" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="총괄11" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="충남신설">#REF!</definedName>
-    <definedName name="충북신설">#REF!</definedName>
-    <definedName name="ㅋ">#REF!</definedName>
-    <definedName name="ㅋㅋ">[6]단계별측정!#REF!</definedName>
-    <definedName name="ㅋㅋㅋ">#REF!</definedName>
     <definedName name="카" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="타" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="특별시방서1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="파" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="표준용어">#REF!</definedName>
-    <definedName name="표준프로세스">#REF!</definedName>
     <definedName name="프로젝트명">"민원시스템 백업장비 도입 및 노후장비 교체"</definedName>
     <definedName name="하" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="한" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="합계">#REF!</definedName>
-    <definedName name="협업포탈_1">'[2]예정(3)'!#REF!</definedName>
     <definedName name="홎ㅅㄱ도" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅏㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ도">#REF!</definedName>
     <definedName name="ㅏ딪" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅏㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ아">#REF!</definedName>
     <definedName name="ㅏ잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅏ짇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅏㅣㄴ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅏㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅓ아ㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅗㄷ">#REF!</definedName>
-    <definedName name="ㅗㅎㄷ">#REF!</definedName>
     <definedName name="ㅜ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅜㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅜ자ㅣㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅠ">#REF!</definedName>
-    <definedName name="ㅠㄹㅇ">#REF!</definedName>
     <definedName name="ㅣ닺" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅣㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅣㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -691,13 +473,7 @@
     <definedName name="ㅣㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅣ잗" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅣ젇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_" localSheetId="2">#REF!</definedName>
-    <definedName name="__" localSheetId="2">#REF!</definedName>
-    <definedName name="_80486SX_25" localSheetId="2">[1]COST!#REF!</definedName>
     <definedName name="_kwy1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_Table1_In1" localSheetId="2" hidden="1">#REF!</definedName>
-    <definedName name="_Table1_Out" localSheetId="2" hidden="1">#REF!</definedName>
-    <definedName name="AA" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="cwe" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="D" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="DJDJDJDJ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -706,18 +482,12 @@
     <definedName name="dklw" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="dkw" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="dsfga" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="EI_A" localSheetId="2">IF( OR(AND(#REF!&lt;2,#REF!&gt;50), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 20,#REF!&lt;= 50)), AND(#REF!&gt;5, AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
-    <definedName name="EI_C" localSheetId="2">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=5),#REF!&gt; 50), AND(#REF!&gt;5,#REF!&gt;=  20) ),1,0)</definedName>
-    <definedName name="EI_S" localSheetId="2">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 50)), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
     <definedName name="er" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="fkwheku" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="FT_A" localSheetId="2">IF( OR(AND(#REF!&lt;2,#REF!&gt;50), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 20,#REF!&lt;= 50)), AND(#REF!&gt;5, AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
     <definedName name="gfdsdfg" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="H" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="hejlkw" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="hsdgfjhf" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="IT_A" localSheetId="2">IF( OR(AND(#REF!&lt;2,#REF!&gt;15), AND(#REF!=2, AND(#REF!&gt;= 5,#REF!&lt;= 15)), AND(#REF!&gt;2, AND(#REF!&gt;=1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="IT_C" localSheetId="2">IF( OR(AND(#REF!=2,#REF!&gt; 15), AND(#REF!&gt;2,#REF!&gt;=  5) ),1,0)</definedName>
     <definedName name="IWFIC" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jdkl" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jeklw" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -731,11 +501,7 @@
     <definedName name="kwy" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="PERT" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="qq" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="QT_A" localSheetId="2">IF( OR(AND(#REF!&lt;2,#REF!&gt;19), AND(AND(#REF!&gt;=2,#REF!&lt;= 3), AND(#REF!&gt;= 6,#REF!&lt;= 19)), AND(#REF!&gt;3, AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
-    <definedName name="rr" localSheetId="2" hidden="1">#REF!</definedName>
-    <definedName name="RRR" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="s" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="SS" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="TOTAL" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vbkjwhe" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vdwf" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -824,7 +590,6 @@
     <definedName name="아ㅓㅗㄹ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈㅂ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="이름" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="일일대가1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="잊" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅈ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -864,9 +629,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'요구사항정의서_전체'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'요구사항정의서_전체'!$B$1:$Q$137</definedName>
     <definedName name="_kwy1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_Table1_In1" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="_Table1_Out" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="AA" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="cwe" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="D" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="DJDJDJDJ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -894,10 +656,7 @@
     <definedName name="kwy" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="PERT" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="qq" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="rr" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="RRR" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="s" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="SS" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="TOTAL" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vbkjwhe" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vdwf" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -984,7 +743,6 @@
     <definedName name="아ㅓㅗㄹ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈㅂ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="이름" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="일일대가1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="잊" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅈ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -1024,9 +782,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'요구사항정의서_기능'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'요구사항정의서_기능'!$B$1:$Q$65</definedName>
     <definedName name="_kwy1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_Table1_In1" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="_Table1_Out" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="AA" localSheetId="4" hidden="1">#REF!</definedName>
     <definedName name="cwe" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="D" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="DJDJDJDJ" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -1054,10 +809,7 @@
     <definedName name="kwy" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="PERT" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="qq" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="rr" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="RRR" localSheetId="4" hidden="1">#REF!</definedName>
     <definedName name="s" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="SS" localSheetId="4" hidden="1">#REF!</definedName>
     <definedName name="TOTAL" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vbkjwhe" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vdwf" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -1144,7 +896,6 @@
     <definedName name="아ㅓㅗㄹ" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈ" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈㅂ" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="이름" localSheetId="4" hidden="1">#REF!</definedName>
     <definedName name="일일대가1" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="잊" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅈ" localSheetId="4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -2581,481 +2332,6 @@
 </wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="COST"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="요약"/>
-      <sheetName val="SIZE"/>
-      <sheetName val="SIZE_DETAIL"/>
-      <sheetName val="운영현황보고(6월)"/>
-      <sheetName val="Summary"/>
-      <sheetName val="유형별CSR처리현황"/>
-      <sheetName val="등급(처리시간)별 CSR 처리현황"/>
-      <sheetName val="주별 CSR 처리현황"/>
-      <sheetName val="유형별 CSR 분석(모듈)"/>
-      <sheetName val="규모,공수분석"/>
-      <sheetName val="기타 공수분석"/>
-      <sheetName val="CCR(최대CPU사용율)"/>
-      <sheetName val="CCR(평균CPU사용율)"/>
-      <sheetName val="CCR(최대PAGING SPACE IO"/>
-      <sheetName val="CCR(디스크사용량)"/>
-      <sheetName val="CSR납기분석"/>
-      <sheetName val="inspection_data(5월)"/>
-      <sheetName val="inspection_data(6월)"/>
-      <sheetName val="결함유형분석"/>
-      <sheetName val="결함종류별 분석"/>
-      <sheetName val="TEST결함관리"/>
-      <sheetName val="Inspection summary"/>
-      <sheetName val="위험문제관리"/>
-      <sheetName val="구성관리(실적)"/>
-      <sheetName val="SQA"/>
-      <sheetName val="교육"/>
-      <sheetName val="2003년도_교육계획(안)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Calc V1.2 (2)"/>
-      <sheetName val="Calc V1.2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="ILF &amp; EIF"/>
-      <sheetName val="EI"/>
-      <sheetName val="EQ"/>
-      <sheetName val="EO"/>
-      <sheetName val="FPA"/>
-      <sheetName val="Package (In-House)"/>
-      <sheetName val="In House"/>
-      <sheetName val="VAF"/>
-      <sheetName val="순수개발"/>
-      <sheetName val="Macro상수지정"/>
-      <sheetName val="Config"/>
-      <sheetName val="Package (by ITSA)"/>
-      <sheetName val="Dialog1"/>
-      <sheetName val="Module1"/>
-      <sheetName val="Module2"/>
-      <sheetName val="영남_1"/>
-      <sheetName val="견적990322"/>
-      <sheetName val="20관리비율"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="노임"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="fpa_dev(dev)"/>
-      <sheetName val="Data Vol"/>
-      <sheetName val="FPA"/>
-      <sheetName val="순수개발"/>
-      <sheetName val="ilch"/>
-      <sheetName val="Galaxy 소비자가격표"/>
-      <sheetName val="공사내역"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="개정이력"/>
-      <sheetName val="기본정보"/>
-      <sheetName val="Data"/>
-      <sheetName val="Transaction"/>
-      <sheetName val="FPA_검증"/>
-      <sheetName val="VAF"/>
-      <sheetName val="공수견적"/>
-      <sheetName val="비용산정"/>
-      <sheetName val="품질항목"/>
-      <sheetName val="CountingTip"/>
-      <sheetName val="Macro상수"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="요약"/>
-      <sheetName val="SIZE"/>
-      <sheetName val="SIZE_DETAIL"/>
-      <sheetName val="운영현황보고(5월)"/>
-      <sheetName val="Summary"/>
-      <sheetName val="유형별CSR처리현황"/>
-      <sheetName val="주별 CSR 처리현황"/>
-      <sheetName val="유형별 CSR 분석(모듈)"/>
-      <sheetName val="SAP등록 건 확인(5월)"/>
-      <sheetName val="규모,공수분석"/>
-      <sheetName val="기타 공수분석"/>
-      <sheetName val="CCR(최대CPU사용율)"/>
-      <sheetName val="CCR(평균CPU사용율)"/>
-      <sheetName val="CCR(최대PAGING SPACE IO"/>
-      <sheetName val="CCR(평균PAGING SPACE IO"/>
-      <sheetName val="CCR(디스크사용량)"/>
-      <sheetName val="CCE(디스크사용량_DATA)"/>
-      <sheetName val="CSR납기분석"/>
-      <sheetName val="결함분석(누적)"/>
-      <sheetName val="inspection_data(5월)"/>
-      <sheetName val="Inspection summary"/>
-      <sheetName val="위험문제관리"/>
-      <sheetName val="Test"/>
-      <sheetName val="구성관리(실적)"/>
-      <sheetName val="SQA"/>
-      <sheetName val="교육"/>
-      <sheetName val="2003년도_교육계획(안)"/>
-      <sheetName val="08.Lessons Learned"/>
-      <sheetName val="1.요약"/>
-      <sheetName val="2.일정추적"/>
-      <sheetName val="3.규모추적"/>
-      <sheetName val="4.1공수분석_개발"/>
-      <sheetName val="4.2공수추적_관리"/>
-      <sheetName val="5.1결함분석_현황"/>
-      <sheetName val="5.2결함분석_제거"/>
-      <sheetName val="6.Risks"/>
-      <sheetName val="7.실시내용 &amp; Issues"/>
-      <sheetName val="8.Lessons"/>
-      <sheetName val="99.1공수"/>
-      <sheetName val="99.2결함"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="예정(3)"/>
-      <sheetName val="동원(3)"/>
-      <sheetName val="공사설명서"/>
-      <sheetName val="주요자재"/>
-      <sheetName val="예정공정표 (2)"/>
-      <sheetName val="동원인원 (2)"/>
-      <sheetName val="예정공정표"/>
-      <sheetName val="동원인원"/>
-      <sheetName val="가설공사"/>
-      <sheetName val="가설울타리"/>
-      <sheetName val="경고테이프"/>
-      <sheetName val="포장절단"/>
-      <sheetName val="FM공법 (2)"/>
-      <sheetName val="FM공법"/>
-      <sheetName val="인수공지수판"/>
-      <sheetName val="양수작업"/>
-      <sheetName val="상수도이설"/>
-      <sheetName val="포장복구(AS,CO)"/>
-      <sheetName val="압입공법"/>
-      <sheetName val="GR보호몰탈"/>
-      <sheetName val="교량첨가"/>
-      <sheetName val="피스표(수정)"/>
-      <sheetName val="피스표(수도)"/>
-      <sheetName val="피스표(4pe)"/>
-      <sheetName val="목차"/>
-      <sheetName val="소요노력"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="9GNG운반"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="프로젝트정보"/>
-      <sheetName val="크기추정"/>
-      <sheetName val="공수추정"/>
-      <sheetName val="단계별측정"/>
-      <sheetName val="검토측정"/>
-      <sheetName val="변경측정"/>
-      <sheetName val="문서크기측정"/>
-      <sheetName val="소스코드크기측정"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="COST"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="단계별측정"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="산출"/>
-      <sheetName val="OUT"/>
-      <sheetName val="IN"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="IN"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="main"/>
-      <sheetName val="DATA"/>
-      <sheetName val="ELEC"/>
-      <sheetName val="Raw"/>
-      <sheetName val="발생"/>
-      <sheetName val="평가"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/Audit/JJ_PM_SC02_요구사항정의서_v1.4_20261028_이노팸.xlsx
+++ b/Audit/JJ_PM_SC02_요구사항정의서_v1.4_20261028_이노팸.xlsx
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>화면설계서 v1.5 검수본 반영: 메뉴 명칭 현행화(불법 주차 집중 구역 분석·정책 효과 시뮬레이션·구역추천·대시보드), 격자 크기(100m~1km), 예측 기간 삭제, 알림 기준 설정 팝업, 구역추천 해결방안 현행화, AI 모델 표기(Gemma)</t>
+          <t>화면설계서 v1.5 검수본 반영: 메뉴 명칭 현행화(불법 주차 집중 구역 분석·정책 효과 시뮬레이션·구역추천·대시보드), 격자 크기(100m~1km), 예측 기간 삭제, 알림 기준 설정 팝업, 구역추천 해결방안 현행화, AI 모델 표기(Gemma), 민원현황 히트맵 표현 전환·AI 조례 응답 방식 현행화</t>
         </is>
       </c>
       <c r="D6" s="33" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="J15" s="59" t="inlineStr">
         <is>
-          <t>○ 민원 발생 현황·패턴을 제주 전역 히트맵과 읍·면·동 집계 순위로 시각화하여 '민원현황' 화면에 구현
+          <t>○ 민원 발생 현황·패턴을 제주 전역 히트맵(민원 건수 밀도)과 읍·면·동 집계 순위로 시각화하여 '민원현황' 화면에 구현 — 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵 표현 전환 지원
 ○ 읍·면·동 비교카드(건수·증감율·유형 세분화)로 '대시보드'에 구현</t>
         </is>
       </c>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="J21" s="59" t="inlineStr">
         <is>
-          <t>○ 민원 다발지역·단속 집중지역·수요 부족지역을 레이어 선택 기반 히트맵과 KPI 카드·범례로 GIS 시각화하여 '민원현황' 화면에 구현</t>
+          <t>○ 민원 다발지역·단속 집중지역·수요 부족지역을 레이어 선택 기반으로 GIS 시각화하여 '민원현황' 화면에 구현 — 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환, 등급·그라데이션 범례 제공</t>
         </is>
       </c>
       <c r="K21" s="51" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="J45" s="59" t="inlineStr">
         <is>
-          <t>○ sLLM·RAG 기반 정책문서·조례 검색 및 행정 Q&amp;A·보고서 작성 지원을 'AI 어시스턴트'로 구현</t>
+          <t>○ sLLM·RAG 기반 정책문서·조례 검색 및 행정 Q&amp;A·보고서 작성 지원을 'AI 어시스턴트'로 구현 — 조례 질의 시 조례명·관련 조문 발췌로 응답</t>
         </is>
       </c>
       <c r="K45" s="51" t="inlineStr">

--- a/Audit/JJ_PM_SC02_요구사항정의서_v1.4_20261028_이노팸.xlsx
+++ b/Audit/JJ_PM_SC02_요구사항정의서_v1.4_20261028_이노팸.xlsx
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>화면설계서 v1.5 검수본 반영: 메뉴 명칭 현행화(불법 주차 집중 구역 분석·정책 효과 시뮬레이션·구역추천·대시보드), 격자 크기(100m~1km), 예측 기간 삭제, 알림 기준 설정 팝업, 구역추천 해결방안 현행화, AI 모델 표기(Gemma), 민원현황 히트맵 표현 전환·AI 조례 응답 방식 현행화</t>
+          <t>화면설계서 v1.5 검수본 반영: 메뉴 명칭 현행화(불법 주차 집중 구역 분석·정책 효과 시뮬레이션·구역추천·대시보드), 격자 크기(100m~1km), 예측 기간 삭제, 알림 기준 설정 팝업, 구역추천 해결방안 현행화, AI 모델 표기(Gemma)</t>
         </is>
       </c>
       <c r="D6" s="33" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="J15" s="59" t="inlineStr">
         <is>
-          <t>○ 민원 발생 현황·패턴을 제주 전역 히트맵(민원 건수 밀도)과 읍·면·동 집계 순위로 시각화하여 '민원현황' 화면에 구현 — 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵 표현 전환 지원
+          <t>○ 민원 발생 현황·패턴을 제주 전역 히트맵과 읍·면·동 집계 순위로 시각화하여 '민원현황' 화면에 구현
 ○ 읍·면·동 비교카드(건수·증감율·유형 세분화)로 '대시보드'에 구현</t>
         </is>
       </c>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="J21" s="59" t="inlineStr">
         <is>
-          <t>○ 민원 다발지역·단속 집중지역·수요 부족지역을 레이어 선택 기반으로 GIS 시각화하여 '민원현황' 화면에 구현 — 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환, 등급·그라데이션 범례 제공</t>
+          <t>○ 민원 다발지역·단속 집중지역·수요 부족지역을 레이어 선택 기반 히트맵과 KPI 카드·범례로 GIS 시각화하여 '민원현황' 화면에 구현</t>
         </is>
       </c>
       <c r="K21" s="51" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="J45" s="59" t="inlineStr">
         <is>
-          <t>○ sLLM·RAG 기반 정책문서·조례 검색 및 행정 Q&amp;A·보고서 작성 지원을 'AI 어시스턴트'로 구현 — 조례 질의 시 조례명·관련 조문 발췌로 응답</t>
+          <t>○ sLLM·RAG 기반 정책문서·조례 검색 및 행정 Q&amp;A·보고서 작성 지원을 'AI 어시스턴트'로 구현</t>
         </is>
       </c>
       <c r="K45" s="51" t="inlineStr">
